--- a/Result/profitability/3558.xlsx
+++ b/Result/profitability/3558.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM71"/>
+  <dimension ref="A1:AM72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -668,7 +668,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>19.15875</v>
+        <v>18.82125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -777,7 +777,7 @@
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>20.62875</v>
+        <v>20.27</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -890,7 +890,7 @@
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>22.45625</v>
+        <v>22.3025</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>23.80875</v>
+        <v>23.91</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>25.605</v>
+        <v>25.82625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>27.51</v>
+        <v>27.79375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>29.2675</v>
+        <v>29.31625</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1619,7 +1619,7 @@
         <v>1.04</v>
       </c>
       <c r="M10" t="n">
-        <v>0.8137500000000001</v>
+        <v>0.81375</v>
       </c>
       <c r="N10" t="n">
         <v>29.26625</v>
@@ -9419,6 +9419,133 @@
       </c>
       <c r="AM71" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>3558</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>3569</v>
+      </c>
+      <c r="D72" t="n">
+        <v>2976</v>
+      </c>
+      <c r="E72" t="n">
+        <v>594</v>
+      </c>
+      <c r="F72" t="n">
+        <v>16.63</v>
+      </c>
+      <c r="G72" t="n">
+        <v>63</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>1.77%</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>10</v>
+      </c>
+      <c r="J72" t="n">
+        <v>73</v>
+      </c>
+      <c r="K72" t="n">
+        <v>42</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="M72" t="n">
+        <v>1.15875</v>
+      </c>
+      <c r="N72" t="n">
+        <v>16.825</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
+      </c>
+      <c r="V72" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W72" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="X72" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>0.3900000000000006</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>0.02401477832512322</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>-0.5800000000000001</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>-0.4496124031007752</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>0.8099999999999987</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>0.05120101137800237</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK72" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
